--- a/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
@@ -595,7 +595,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What does `packing_list[-1]` return for packing_list = ["water bottle", "charger", "ID card"]?</t>
+          <t>A travel-packing app keeps a list of items a traveler has packed and needs to quickly check the last item added.
+What does `packing_list[-1]` return for packing_list = ["water bottle", "charger", "ID card"]?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -673,7 +674,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A packing checklist app lets a user add one more snack item to their travel list.
+```python
 snacks = ["chips", "biscuits"]
 snacks.append("juice boxes")
 print(snacks)
@@ -1502,7 +1504,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which line correctly creates a list holding three city names?</t>
+          <t>A travel-planning app needs to store three cities a user plans to visit on their trip.
+Which line correctly creates a list holding three city names?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1580,7 +1583,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A packing-checklist app displays a specific item from a traveler's saved list.
+```python
 packing_list = ["water bottle", "charger", "ID card", "raincoat", "snacks"]
 print(packing_list[2])
 ```
@@ -1822,7 +1826,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A packing-checklist app tries to display an item at a position beyond the end of a traveler's short list.
+```python
 packing_list = ["water bottle", "charger", "ID card"]
 print(packing_list[10])
 ```
@@ -2070,7 +2075,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the key difference between `list.append(value)` and `list.insert(0, value)`?</t>
+          <t>A packing-checklist app lets a user add an item either to the end of the list or insert it at the very front.
+What is the key difference between `list.append(value)` and `list.insert(0, value)`?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2226,7 +2232,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A snack-vending app removes and returns the last item from a queue of available snacks.
+```python
 snacks = ["fruit", "chips", "juice boxes"]
 last_item = snacks.pop()
 print(last_item, snacks)
@@ -2493,7 +2500,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A ticket-counter queue app reverses the order of waiting customers before calling them in.
+```python
 queue = ["Asha", "Ravi", "Meera"]
 queue.reverse()
 print(queue)
@@ -2576,7 +2584,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A gradebook app ranks student scores from highest to lowest for a leaderboard.
+```python
 scores = [72, 95, 60, 88]
 scores.sort(reverse=True)
 print(scores)
@@ -3066,7 +3075,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A shopping app filters a list of item quantities to find only the even-numbered ones for a bulk discount.
+```python
 numbers = [3, 8, 5, 12, 7, 10]
 evens = [n for n in numbers if n % 2 == 0]
 print(evens)
@@ -3334,7 +3344,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which line correctly creates a tuple holding two coordinate values?</t>
+          <t>A mapping app needs to store a fixed pair of latitude and longitude coordinates for a landmark.
+Which line correctly creates a tuple holding two coordinate values?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3412,7 +3423,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What is the type of the value x = (5)?</t>
+          <t>A travel app stores a single GPS reading and a developer wants to confirm it was actually saved as a tuple.
+What is the type of the value x = (5)?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3573,7 +3585,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A travel app stores a resort's fixed GPS coordinates as a tuple and a bug tries to update one value after booking.
+```python
 resort = (15.2993, 74.1240)
 resort[0] = 16.0
 ```
@@ -3737,7 +3750,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A travel app unpacks a saved tourist-stop record into separate name and coordinate variables.
+```python
 stop = ("Dudhsagar Falls", 15.3144, 74.3144)
 name, lat, long = stop
 print(lat)

--- a/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 6.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 6.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 6.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 6.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 6.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 6.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 6.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 6.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -728,26 +728,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>['chips', 'biscuits', 'juice boxes']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>['juice boxes', 'chips', 'biscuits']</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>`None` returned</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>['chips', 'biscuits'] unchanged</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>['chips', 'biscuits', 'juice boxes']</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>['juice boxes', 'chips', 'biscuits']</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -806,26 +806,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>(expression for item in sequence if condition)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[if condition: expression for item in sequence]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>[for item in sequence if condition: expression]</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>[expression for item in sequence if condition]</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>(expression for item in sequence if condition)</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>[for item in sequence if condition: expression]</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>[if condition: expression for item in sequence]</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -884,26 +884,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Will the contents need to change after creation?</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Will the data be printed more than once?</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Is the collection longer than five items?</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Does the data contain numbers?</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Is the collection longer than five items?</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Will the contents need to change after creation?</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Will the data be printed more than once?</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -962,26 +962,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>remove deletes by value, pop deletes by position and returns the removed item</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>They are exactly the same method under a different name</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>pop can technically only ever remove the very first item</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>remove deletes by value, pop deletes by position and returns the removed item</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>They are exactly the same method under a different name</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>remove technically returns the removed item, but pop does not</t>
+          <t>remove technically returns the removed item on every call, but pop does not</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1045,26 +1045,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>[110, 275, 82.5]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[100, 250, 75]</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>[90.0, 225.0, 67.5]</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>An error, since no filter is present</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>[100, 250, 75]</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>[110, 275, 82.5]</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1123,26 +1123,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>A set, since the order of values does not matter here</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>A string, since both values can simply be joined together</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>A tuple, since it documents that the values are fixed and related</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>A set, since the order of values does not matter here</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>A list, since it is generally considered more flexible</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1210,21 +1210,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Meera</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Riya</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Meera</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Kabir</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1289,22 +1289,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>An error occurs, since snacks is now considered undefined</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>['chips', 'biscuits', 'water'], because both names reference the same list</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>['chips', 'biscuits'], left completely unchanged as before</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>['water'], since official_list completely overwrote the snacks list</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>['chips', 'biscuits', 'water'], because both names reference the same list</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>['chips', 'biscuits'], left completely unchanged as before</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>An error occurs, since snacks is now considered undefined</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1378,21 +1378,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0 0, since both variables somehow get overwritten with zero</t>
+          <t>10 5, because the right side is packed into a tuple before unpacking into a and b</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>10 5, because the right side is packed into a tuple before unpacking into a and b</t>
+          <t>An error, since simultaneous assignment is not allowed</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>An error, since simultaneous assignment is not allowed</t>
+          <t>0 0, since both variables somehow get quietly overwritten with zero</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1553,14 +1553,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>cities = ["Goa", "Pune", "Delhi"]</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>`cities = "Goa"`, "Pune", "Delhi"</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>cities = ["Goa", "Pune", "Delhi"]</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>cities = ("Goa", "Pune", "Delhi")</t>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1636,26 +1636,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>ID card</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>water bottle</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>raincoat</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ID card</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>charger</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>water bottle</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1718,17 +1718,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>[10, 20, 30]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[20, 30]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>[20, 30, 40]</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>[20, 30]</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>[10, 20, 30]</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>A list places no restriction on the types of values it holds</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Only the first item's type is enforced for the rest</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>A list places no restriction on the types of values it holds</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Python silently converts everything to strings</t>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1879,22 +1879,22 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Wraps around to index 0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Prints an empty string</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Raises an `IndexError`</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Prints `None`</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Prints an empty string</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Raises an `IndexError`</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Wraps around to index 0</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>['chips', 'juice'] gets printed together as one combined list</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>`None`, because append returns nothing and the original list is discarded</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>['chips'] gets printed back completely unchanged</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>`None`, because append returns nothing and the original list is discarded</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>['chips', 'juice'] gets printed together as one combined list</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2045,26 +2045,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>['Sapphire', 'Anthem', 'Bassline'], unchanged</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>`None`, because `sort()` returns nothing useful</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>An error is raised</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>['Sapphire', 'Anthem', 'Bassline'], unchanged</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>['Anthem', 'Bassline', 'Sapphire']</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>insert technically only ever works correctly on tuples</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>append technically removes the very last item first</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>They behave in exactly an identical way every time</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>insert technically only ever works correctly on tuples</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>append technically removes the very last item first</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2202,26 +2202,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>new_list = old_list = []</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>new_list = `old_list.copy()`</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>new_list = `old_list[0]`</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>new_list = old_list</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>new_list = `old_list[0]`</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>new_list = old_list = []</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>new_list = `old_list.copy()`</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2286,26 +2286,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>juice boxes ['fruit', 'chips', 'juice boxes']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>`None` ['fruit', 'chips']</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>fruit ['chips', 'juice boxes']</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>juice boxes ['fruit', 'chips']</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>`None` ['fruit', 'chips']</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>fruit ['chips', 'juice boxes']</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>juice boxes ['fruit', 'chips', 'juice boxes']</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2470,22 +2470,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>['Anthem', 'Bassline', 'Sapphire']</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>['Sapphire', 'Anthem', 'Bassline']</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>['Bassline', 'Anthem', 'Sapphire']</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>`None`</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>['Sapphire', 'Anthem', 'Bassline']</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>['Bassline', 'Anthem', 'Sapphire']</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>['Anthem', 'Bassline', 'Sapphire']</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2554,26 +2554,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>['Asha', 'Meera', 'Ravi']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>['Asha', 'Ravi', 'Meera']</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>['Meera', 'Ravi', 'Asha']</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>['Asha', 'Meera', 'Ravi']</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>['Asha', 'Ravi', 'Meera']</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sorted alphabetically descending</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2638,26 +2638,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>[95, 88, 72, 60]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>`None`</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>[95, 88, 72, 60]</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>[72, 95, 60, 88]</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>[60, 72, 88, 95]</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>[72, 95, 60, 88]</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2721,26 +2721,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>['Meera', 'Kabir']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>['Asha']</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>['ravi', 'MEERA', 'kabir']</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>['Meera', 'Kabir']</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>['Asha', 'Ravi', 'Meera', 'Kabir']</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2799,26 +2799,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Keep packing more logic into the one-liner regardless of readability</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Switch back to a plain for loop for clarity</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Comprehensions cannot contain conditions, so this is impossible</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Convert it to a tuple instead</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Keep packing more logic into the one-liner regardless of readability</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Switch back to a plain for loop for clarity</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2963,26 +2963,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2 3</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3 3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4 3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>3 4</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2 3</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>3 3</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>4 3</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Prints the number 2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>Prints `None` back</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Prints the number 2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -3129,26 +3129,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>[3, 8, 5, 12, 7, 10]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>[3, 5, 7]</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>[8, 12, 10]</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>[3, 8, 5, 12, 7, 10]</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -3213,26 +3213,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3393,14 +3393,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>resort = (15.2993, 74.1240)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>resort = {15.2993, 74.1240}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>resort = (15.2993, 74.1240)</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>`resort = 15.2993`; 74.1240</t>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3472,26 +3472,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>tuple</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>`TypeError`</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>list</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>tuple</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>`TypeError`</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3638,26 +3638,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>It converts the tuple into a list first</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>It raises a `TypeError`</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>It converts the tuple into a list first</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>It silently does nothing</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>It updates the first value successfully</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>It silently does nothing</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>&lt;class 'list'&gt;</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>`SyntaxError`</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>&lt;class 'list'&gt;</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -3804,26 +3804,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>An error</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>74.3144</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Dudhsagar Falls</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>15.3144</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Dudhsagar Falls</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>An error</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>74.3144</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>(90, 85)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>An error, nested unpacking is not supported</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>(90, 85)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3969,14 +3969,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>The outer list can grow while each individual stop record stays fixed</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Tuples inside a list automatically become lists</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>It is required syntax, lists cannot hold plain values</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>It prevents the list itself from ever changing</t>
@@ -3984,11 +3984,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>The outer list can grow while each individual stop record stays fixed</t>
+          <t>It is required syntax; lists cannot hold plain values at all</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4052,26 +4052,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>An error, nested lists cannot be mutated</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[['Asha', 'Aman'], ['Kabir', 'Dev']]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>[['Asha', 'Ravi'], ['Kabir', 'Dev']]</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>[['Asha', 'Ravi'], ['Kabir', 'Aman']]</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>[['Asha', 'Aman'], ['Kabir', 'Dev']]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>An error, nested lists cannot be mutated</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>`rows[0][0]` = 9 actually changes every single list in the whole program</t>
+          <t>Both rows reference the same inner list object, so the inner list is shared, not duplicated</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Both rows reference the same inner list object, so the inner list is shared, not duplicated</t>
+          <t>`rows[0][0]` = 9 actually changes every single list in the whole program permanently</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
@@ -596,7 +596,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>A travel-packing app keeps a list of items a traveler has packed and needs to quickly check the last item added.
-What does `packing_list[-1]` return for packing_list = ["water bottle", "charger", "ID card"]?</t>
+What does `packing_list[-1]` return for `packing_list` = ["water bottle", "charger", "ID card"]?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assigning a list to a new variable does not copy it; both names point to the same underlying list in memory, so appending through official_list also changes what snacks sees, printing ['chips', 'biscuits', 'water'].</t>
+          <t>Assigning a list to a new variable does not copy it; both names point to the same underlying list in memory, so appending through `official_list` also changes what snacks sees, printing ['chips', 'biscuits', 'water'].</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>['water'], since official_list completely overwrote the snacks list</t>
+          <t>['water'], since `official_list` completely overwrote the snacks list</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why does Python allow trip_info = ["Goa", 3, 4500.50, `True`] without error?</t>
+          <t>Why does Python allow `trip_info` = ["Goa", 3, 4500.50, `True`] without error?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2202,22 +2202,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>new_list = old_list = []</t>
+          <t>`new_list` = `old_list` = []</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>new_list = `old_list.copy()`</t>
+          <t>`new_list` = `old_list.copy()`</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>new_list = `old_list[0]`</t>
+          <t>`new_list` = `old_list[0]`</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>new_list = old_list</t>
+          <t>`new_list` = `old_list`</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Called with no argument, pop removes and returns the last item of the list, so last_item is 'juice boxes' and snacks becomes ['fruit', 'chips'].</t>
+          <t>Called with no argument, pop removes and returns the last item of the list, so `last_item` is 'juice boxes' and snacks becomes ['fruit', 'chips'].</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - MCQ.xlsx
@@ -806,22 +806,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>(expression for item in sequence if condition)</t>
+          <t>`(expression for item in sequence if condition)`</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[if condition: expression for item in sequence]</t>
+          <t>`[if condition: expression for item in sequence]`</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[for item in sequence if condition: expression]</t>
+          <t>`[for item in sequence if condition: expression]`</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[expression for item in sequence if condition]</t>
+          <t>`[expression for item in sequence if condition]`</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The right side b, a packs the current values into a temporary tuple (10, 5) before any assignment happens, and that tuple is then unpacked into a and b, so a becomes 10 and b becomes 5, a clean swap with no temporary variable needed.</t>
+          <t>The right side `b, a` packs the current values into a temporary tuple `(10, 5)` before any assignment happens, and that tuple is then unpacked into `a` and `b`, so `a` becomes `10` and `b` becomes `5` — a clean swap with no temporary variable needed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1553,22 +1553,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>cities = ["Goa", "Pune", "Delhi"]</t>
+          <t>`cities = ["Goa", "Pune", "Delhi"]`</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>`cities = "Goa"`, "Pune", "Delhi"</t>
+          <t>`cities = "Goa", "Pune", "Delhi"`</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>cities = ("Goa", "Pune", "Delhi")</t>
+          <t>`cities = ("Goa", "Pune", "Delhi")`</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>cities = {"Goa", "Pune", "Delhi"}</t>
+          <t>`cities = {"Goa", "Pune", "Delhi"}`</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why does Python allow `trip_info` = ["Goa", 3, 4500.50, `True`] without error?</t>
+          <t>Why does Python allow `trip_info = ["Goa", 3, 4500.50, True]` without error?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3393,22 +3393,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>resort = (15.2993, 74.1240)</t>
+          <t>`resort = (15.2993, 74.1240)`</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>resort = {15.2993, 74.1240}</t>
+          <t>`resort = {15.2993, 74.1240}`</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>`resort = 15.2993`; 74.1240</t>
+          <t>`resort = 15.2993; 74.1240`</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>resort = [15.2993, 74.1240]</t>
+          <t>`resort = [15.2993, 74.1240]`</t>
         </is>
       </c>
       <c r="Q2" t="n">
